--- a/artfynd/A 8319-2025 artfynd.xlsx
+++ b/artfynd/A 8319-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119697530</v>
+        <v>119697663</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430961</v>
+        <v>431031</v>
       </c>
       <c r="R2" t="n">
-        <v>6500412</v>
+        <v>6500422</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119697767</v>
+        <v>119956891</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100053</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,24 +818,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörsås, Vg</t>
+          <t>Rävaberget, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430979</v>
+        <v>431115</v>
       </c>
       <c r="R3" t="n">
-        <v>6500428</v>
+        <v>6500521</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,17 +899,17 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eric Bjuringer</t>
+          <t>Johan Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eric Bjuringer</t>
+          <t>Via Johan Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
     </row>
@@ -908,16 +918,11 @@
         <v>119697802</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1020,37 +1025,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119956893</v>
+        <v>119697765</v>
       </c>
       <c r="B5" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100053</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,34 +1058,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rävaberget, Vg</t>
+          <t>Rörsås, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431115</v>
+        <v>430936</v>
       </c>
       <c r="R5" t="n">
-        <v>6500521</v>
+        <v>6500374</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>20:44</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>20:44</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,17 +1119,237 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Nilsson</t>
+          <t>Eric Bjuringer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Nilsson</t>
+          <t>Eric Bjuringer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119697767</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rörsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>430979</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6500428</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ullervad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119697530</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rörsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>430961</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6500412</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ullervad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 8319-2025 artfynd.xlsx
+++ b/artfynd/A 8319-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697663</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119956891</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697802</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697765</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697767</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,8 +1382,21 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>